--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of 1.5 mM CaCl2. Both as delta(F340/F380) versus the preceding baseline. The three samples of each group were prepared from a single culture plate.</t>
+          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of 1.5 mM CaCl2. Both as delta(F340/F380) versus the preceding baseline. The three samples of each group come from three independent cultures.</t>
         </is>
       </c>
     </row>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,11 +1020,6 @@
           <t>rel_expression</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1060,7 +1055,6 @@
       <c r="I2" t="n">
         <v>1.022782938747284</v>
       </c>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1096,7 +1090,6 @@
       <c r="I3" t="n">
         <v>0.967611620142344</v>
       </c>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1132,7 +1125,6 @@
       <c r="I4" t="n">
         <v>1.008701983790398</v>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1168,7 +1160,6 @@
       <c r="I5" t="n">
         <v>1.001734370234696</v>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1204,11 +1195,6 @@
       <c r="I6" t="n">
         <v>1.818186259055118</v>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1244,11 +1230,6 @@
       <c r="I7" t="n">
         <v>1.518345380207591</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1284,11 +1265,6 @@
       <c r="I8" t="n">
         <v>1.90858045006437</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,11 +1300,6 @@
       <c r="I9" t="n">
         <v>2.031436121861929</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1364,7 +1335,6 @@
       <c r="I10" t="n">
         <v>1.033472499899176</v>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1400,7 +1370,6 @@
       <c r="I11" t="n">
         <v>1.04789923837507</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1436,7 +1405,6 @@
       <c r="I12" t="n">
         <v>1.055187953981984</v>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1472,7 +1440,6 @@
       <c r="I13" t="n">
         <v>0.8750879947452087</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1508,11 +1475,6 @@
       <c r="I14" t="n">
         <v>1.714157888456202</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1548,11 +1510,6 @@
       <c r="I15" t="n">
         <v>1.471716715625615</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1588,11 +1545,6 @@
       <c r="I16" t="n">
         <v>1.566451389130095</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1628,11 +1580,6 @@
       <c r="I17" t="n">
         <v>1.969050346674829</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1668,7 +1615,6 @@
       <c r="I18" t="n">
         <v>1.154685531688693</v>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1704,7 +1650,6 @@
       <c r="I19" t="n">
         <v>0.9913730874626632</v>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1740,7 +1685,6 @@
       <c r="I20" t="n">
         <v>1.005212140041474</v>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1776,7 +1720,6 @@
       <c r="I21" t="n">
         <v>0.8690433204285118</v>
       </c>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1812,11 +1755,6 @@
       <c r="I22" t="n">
         <v>2.862945089285228</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1852,11 +1790,6 @@
       <c r="I23" t="n">
         <v>2.963906629820919</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1892,11 +1825,6 @@
       <c r="I24" t="n">
         <v>3.883883697369405</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1932,11 +1860,6 @@
       <c r="I25" t="n">
         <v>3.089771179918305</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1972,7 +1895,6 @@
       <c r="I26" t="n">
         <v>0.9913730874626625</v>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2008,7 +1930,6 @@
       <c r="I27" t="n">
         <v>1.033472499899175</v>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2044,7 +1965,6 @@
       <c r="I28" t="n">
         <v>0.9982686325973916</v>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2080,7 +2000,6 @@
       <c r="I29" t="n">
         <v>0.9777245612102334</v>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2116,11 +2035,6 @@
       <c r="I30" t="n">
         <v>1.941941848684702</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2156,11 +2070,6 @@
       <c r="I31" t="n">
         <v>1.49226111537404</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2196,11 +2105,6 @@
       <c r="I32" t="n">
         <v>1.655767377972946</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2236,11 +2140,6 @@
       <c r="I33" t="n">
         <v>1.824498544489991</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2276,7 +2175,6 @@
       <c r="I34" t="n">
         <v>1.051537280994008</v>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2312,7 +2210,6 @@
       <c r="I35" t="n">
         <v>0.8965773757702972</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2348,7 +2245,6 @@
       <c r="I36" t="n">
         <v>1.066216194416503</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2384,7 +2280,6 @@
       <c r="I37" t="n">
         <v>0.9948148855014215</v>
       </c>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2420,11 +2315,6 @@
       <c r="I38" t="n">
         <v>0.5008671851173484</v>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>DOWN (sig)</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2460,11 +2350,6 @@
       <c r="I39" t="n">
         <v>0.5149484783374492</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>DOWN (sig)</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2500,11 +2385,6 @@
       <c r="I40" t="n">
         <v>0.4974074427507107</v>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>DOWN (sig)</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2540,11 +2420,6 @@
       <c r="I41" t="n">
         <v>0.5043509918951993</v>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>DOWN (sig)</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2580,7 +2455,6 @@
       <c r="I42" t="n">
         <v>0.9090931295275597</v>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2616,7 +2490,6 @@
       <c r="I43" t="n">
         <v>1.191269640425871</v>
       </c>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2652,7 +2525,6 @@
       <c r="I44" t="n">
         <v>0.7914115359988518</v>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2688,7 +2560,6 @@
       <c r="I45" t="n">
         <v>1.166753665732178</v>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2724,11 +2595,6 @@
       <c r="I46" t="n">
         <v>0.8307578929497527</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>DOWN (ns)</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2764,11 +2630,6 @@
       <c r="I47" t="n">
         <v>0.7435491420613253</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>DOWN (ns)</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2804,11 +2665,6 @@
       <c r="I48" t="n">
         <v>0.9542902250321834</v>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>DOWN (ns)</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2844,11 +2700,6 @@
       <c r="I49" t="n">
         <v>0.8307578929497527</v>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>DOWN (ns)</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2884,7 +2735,6 @@
       <c r="I50" t="n">
         <v>1.012203943399157</v>
       </c>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2920,7 +2770,6 @@
       <c r="I51" t="n">
         <v>0.9576032806985754</v>
       </c>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2956,7 +2805,6 @@
       <c r="I52" t="n">
         <v>1.026333783890422</v>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2992,7 +2840,6 @@
       <c r="I53" t="n">
         <v>1.005212140041476</v>
       </c>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3028,11 +2875,6 @@
       <c r="I54" t="n">
         <v>1.901977263335279</v>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3068,11 +2910,6 @@
       <c r="I55" t="n">
         <v>1.523616693518236</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3108,11 +2945,6 @@
       <c r="I56" t="n">
         <v>1.955449122420466</v>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3148,271 +2980,6 @@
       <c r="I57" t="n">
         <v>2.154719391831541</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Kontrol mean</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>shTDP-43 mean</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Yön</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Anlamlılık (beklenen)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Not</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>TRPC1</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1.000207728228681</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1.819137052797252</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Anlamlı artış</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>SOCE bileşeni</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>ORAI1</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1.002911921750359</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1.680344084971685</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Anlamlı artış</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>SOCE bileşeni</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ATP2A3</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1.005078519905336</v>
-      </c>
-      <c r="C61" t="n">
-        <v>3.200126649098464</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Anlamlı artış</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>SERCA3 – ER Ca²⁺</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>1.000209695292366</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1.72861722163042</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Anlamlı artış</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Anti-apoptotik</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1.002286434170557</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.5043935245251769</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Anlamlı azalma</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Pro-apoptotik</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1.014631992921115</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.8398387882482534</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>DOWN</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Azalma (anlamsız)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Pro-apoptotik</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1.000338287007407</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1.88394061777638</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>UP</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Anlamlı artış</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>SOCE – ER Ca²⁺ sensor</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5472,7 +5039,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>WST-1 viability 24 h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5481,13 +5048,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.268</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>0.042</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -5500,7 +5067,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>WST-1 viability 24 h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5509,13 +5076,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0.18</v>
+        <v>116.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.061</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -5524,7 +5091,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>0.000243</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5103,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SOCE delta F340/F380</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5545,13 +5112,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>1.542</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>0.282</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -5564,7 +5131,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SOCE delta F340/F380</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5573,13 +5140,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.245</v>
+        <v>61.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.083</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -5588,19 +5155,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0115</t>
+          <t>2.14e-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6D</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5609,13 +5176,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>0.268</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>0.042</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -5623,12 +5190,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6D</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5637,13 +5204,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>116.8</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>0.061</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -5652,19 +5219,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.000243</t>
+          <t>0.2989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6D</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5673,13 +5240,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>1.542</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>0.282</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -5687,12 +5254,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6D</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5701,13 +5268,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>61.5</v>
+        <v>0.245</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>0.083</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -5716,7 +5283,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.14e-07</t>
+          <t>0.0115</t>
         </is>
       </c>
     </row>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Raw Ct values for the SOCE and apoptosis targets, four biological replicates per group, same RNA set; experiment window 03.06-10.07.2026.</t>
+          <t>Raw Ct values for the four SOCE-associated targets and GAPDH in shTDP-43 cells and the non-targeting (scrambled) shRNA control, four biological replicates per group, same RNA set; experiment window 03.06-10.07.2026.</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of 1.5 mM CaCl2. Both as delta(F340/F380) versus the preceding baseline. The three samples of each group come from three independent cultures.</t>
+          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of 1.5 mM CaCl2. Both as delta(F340/F380) versus the preceding baseline. The three samples of each group come from three independent cultures. The control group is the non-targeting (scrambled) shRNA control.</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 viability, four wells per group, normalised to the mean of the control group at the same time point.</t>
+          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1864,12 +1864,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1881,30 +1881,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>24.93</v>
+        <v>25.64</v>
       </c>
       <c r="F26" t="n">
         <v>19.42</v>
       </c>
       <c r="G26" t="n">
-        <v>5.509999999999998</v>
+        <v>6.219999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.01249999999999929</v>
+        <v>-0.01750000000000096</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9913730874626625</v>
+        <v>1.012203943399157</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1916,30 +1916,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>25.12</v>
+        <v>25.97</v>
       </c>
       <c r="F27" t="n">
         <v>19.67</v>
       </c>
       <c r="G27" t="n">
-        <v>5.449999999999999</v>
+        <v>6.299999999999997</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.04749999999999943</v>
+        <v>0.06249999999999734</v>
       </c>
       <c r="I27" t="n">
-        <v>1.033472499899175</v>
+        <v>0.9576032806985754</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1951,30 +1951,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>24.81</v>
+        <v>25.51</v>
       </c>
       <c r="F28" t="n">
         <v>19.31</v>
       </c>
       <c r="G28" t="n">
-        <v>5.5</v>
+        <v>6.200000000000003</v>
       </c>
       <c r="H28" t="n">
-        <v>0.002500000000001279</v>
+        <v>-0.03749999999999698</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9982686325973916</v>
+        <v>1.026333783890422</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1986,25 +1986,25 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25.08</v>
+        <v>25.78</v>
       </c>
       <c r="F29" t="n">
         <v>19.55</v>
       </c>
       <c r="G29" t="n">
-        <v>5.529999999999998</v>
+        <v>6.23</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03249999999999886</v>
+        <v>-0.007499999999999396</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9777245612102334</v>
+        <v>1.005212140041476</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2021,25 +2021,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>24.02</v>
+        <v>24.79</v>
       </c>
       <c r="F30" t="n">
         <v>19.48</v>
       </c>
       <c r="G30" t="n">
-        <v>4.539999999999999</v>
+        <v>5.309999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9574999999999996</v>
+        <v>-0.9275000000000011</v>
       </c>
       <c r="I30" t="n">
-        <v>1.941941848684702</v>
+        <v>1.901977263335279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2056,25 +2056,25 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>24.31</v>
+        <v>25.02</v>
       </c>
       <c r="F31" t="n">
         <v>19.39</v>
       </c>
       <c r="G31" t="n">
-        <v>4.919999999999998</v>
+        <v>5.629999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5775000000000006</v>
+        <v>-0.6075000000000008</v>
       </c>
       <c r="I31" t="n">
-        <v>1.49226111537404</v>
+        <v>1.523616693518236</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2091,25 +2091,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>24.38</v>
+        <v>24.88</v>
       </c>
       <c r="F32" t="n">
         <v>19.61</v>
       </c>
       <c r="G32" t="n">
-        <v>4.77</v>
+        <v>5.27</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7274999999999991</v>
+        <v>-0.9675000000000002</v>
       </c>
       <c r="I32" t="n">
-        <v>1.655767377972946</v>
+        <v>1.955449122420466</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCL2</t>
+          <t>STIM1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2126,858 +2126,18 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>24.15</v>
+        <v>24.65</v>
       </c>
       <c r="F33" t="n">
         <v>19.52</v>
       </c>
       <c r="G33" t="n">
-        <v>4.629999999999999</v>
+        <v>5.129999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8674999999999997</v>
+        <v>-1.107500000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1.824498544489991</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>03.06.2026</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>25.41</v>
-      </c>
-      <c r="F34" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="G34" t="n">
-        <v>5.989999999999998</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-0.07250000000000156</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.051537280994008</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>11.06.2026</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="F35" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="G35" t="n">
-        <v>6.219999999999999</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.1574999999999989</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.8965773757702972</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>25.06.2026</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>25.28</v>
-      </c>
-      <c r="F36" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="G36" t="n">
-        <v>5.970000000000002</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-0.09249999999999758</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1.066216194416503</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="F37" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="G37" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.007500000000000284</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.9948148855014215</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>04.06.2026</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>26.54</v>
-      </c>
-      <c r="F38" t="n">
-        <v>19.48</v>
-      </c>
-      <c r="G38" t="n">
-        <v>7.059999999999999</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.9974999999999987</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.5008671851173484</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>12.06.2026</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>26.41</v>
-      </c>
-      <c r="F39" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="G39" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.9574999999999996</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.5149484783374492</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>26.68</v>
-      </c>
-      <c r="F40" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="G40" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1.0075</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.4974074427507107</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="F41" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="G41" t="n">
-        <v>7.050000000000001</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.9875000000000007</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.5043509918951993</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>03.06.2026</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>26.72</v>
-      </c>
-      <c r="F42" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="G42" t="n">
-        <v>7.299999999999997</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.1374999999999993</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.9090931295275597</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>11.06.2026</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>26.58</v>
-      </c>
-      <c r="F43" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6.909999999999997</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-0.2525000000000013</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.191269640425871</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>25.06.2026</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="F44" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="G44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.3375000000000021</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.7914115359988518</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>26.49</v>
-      </c>
-      <c r="F45" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="G45" t="n">
-        <v>6.939999999999998</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-0.2225000000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.166753665732178</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>04.06.2026</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>26.91</v>
-      </c>
-      <c r="F46" t="n">
-        <v>19.48</v>
-      </c>
-      <c r="G46" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.2675000000000018</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.8307578929497527</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>12.06.2026</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>26.98</v>
-      </c>
-      <c r="F47" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="G47" t="n">
-        <v>7.59</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.427500000000002</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.7435491420613253</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="F48" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="G48" t="n">
-        <v>7.23</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.06750000000000256</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9542902250321834</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>26.95</v>
-      </c>
-      <c r="F49" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.2675000000000018</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.8307578929497527</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>03.06.2026</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="F50" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="G50" t="n">
-        <v>6.219999999999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.01750000000000096</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1.012203943399157</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>11.06.2026</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>25.97</v>
-      </c>
-      <c r="F51" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="G51" t="n">
-        <v>6.299999999999997</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.06249999999999734</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.9576032806985754</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>25.06.2026</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="F52" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6.200000000000003</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-0.03749999999999698</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1.026333783890422</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>4</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>09.07.2026</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="F53" t="n">
-        <v>19.55</v>
-      </c>
-      <c r="G53" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-0.007499999999999396</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1.005212140041476</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>04.06.2026</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="F54" t="n">
-        <v>19.48</v>
-      </c>
-      <c r="G54" t="n">
-        <v>5.309999999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-0.9275000000000011</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.901977263335279</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>12.06.2026</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>25.02</v>
-      </c>
-      <c r="F55" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="G55" t="n">
-        <v>5.629999999999999</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0.6075000000000008</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.523616693518236</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>26.06.2026</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>24.88</v>
-      </c>
-      <c r="F56" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-0.9675000000000002</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.955449122420466</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STIM1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="F57" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="G57" t="n">
-        <v>5.129999999999999</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-1.107500000000001</v>
-      </c>
-      <c r="I57" t="n">
         <v>2.154719391831541</v>
       </c>
     </row>
@@ -2992,7 +2152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3025,7 +2185,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3043,7 +2203,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3061,7 +2221,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3079,7 +2239,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3169,7 +2329,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3187,7 +2347,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3205,7 +2365,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3223,7 +2383,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3313,7 +2473,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3331,7 +2491,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3349,7 +2509,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3367,7 +2527,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3457,7 +2617,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -3475,7 +2635,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -3493,7 +2653,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -3511,7 +2671,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3591,438 +2751,6 @@
       </c>
       <c r="D33" t="n">
         <v>3.089771179918305</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.9913730874626625</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.033472499899175</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.9982686325973916</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.9777245612102334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.941941848684702</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.49226111537404</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.655767377972946</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>BCL2</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.824498544489991</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.051537280994008</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.8965773757702972</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.066216194416503</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.9948148855014215</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.5008671851173484</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.5149484783374492</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.4974074427507107</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>BAK1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.5043509918951993</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.9090931295275597</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.191269640425871</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.7914115359988518</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>4</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.166753665732178</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.8307578929497527</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.7435491420613253</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.9542902250321834</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BAX</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>4</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.8307578929497527</v>
       </c>
     </row>
   </sheetData>
@@ -4069,7 +2797,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4087,7 +2815,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4105,7 +2833,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4177,7 +2905,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4195,7 +2923,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4213,7 +2941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4321,7 +3049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4339,7 +3067,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4357,7 +3085,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4375,7 +3103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4465,7 +3193,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4483,7 +3211,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4501,7 +3229,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4519,7 +3247,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4788,7 +3516,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4852,7 +3580,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4916,7 +3644,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4980,7 +3708,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5044,7 +3772,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -5108,7 +3836,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -5172,7 +3900,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -5236,7 +3964,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Non-targeting shRNA control</t>
         </is>
       </c>
       <c r="D20" t="n">

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point.</t>
+          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
         </is>
       </c>
     </row>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
+          <t>WST-1 viability 48 h after seeding, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control. The experiment was performed three times; these are the four wells of one experiment.</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3044,7 +3044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3056,13 +3056,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>97.3063973063973</v>
+        <v>97.47596153846155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3074,13 +3074,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>103.7037037037037</v>
+        <v>102.6442307692308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3092,13 +3092,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>97.97979797979798</v>
+        <v>98.4375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3110,13 +3110,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>101.010101010101</v>
+        <v>101.4423076923077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3128,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>113.8047138047138</v>
+        <v>59.85576923076923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3146,13 +3146,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8754208754209</v>
+        <v>63.46153846153847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3164,13 +3164,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>114.8148148148148</v>
+        <v>60.45673076923077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3182,150 +3182,6 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>117.8451178451178</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>97.47596153846155</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>102.6442307692308</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>98.4375</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>101.4423076923077</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>59.85576923076923</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>63.46153846153847</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>60.45673076923077</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
         <v>62.3798076923077</v>
       </c>
     </row>
@@ -3340,7 +3196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3767,7 +3623,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3782,7 +3638,7 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -3795,7 +3651,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3807,10 +3663,10 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>116.8</v>
+        <v>61.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3819,19 +3675,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.000243</t>
+          <t>2.14e-07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3840,13 +3696,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0.268</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>0.042</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -3854,12 +3710,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>6E</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3868,13 +3724,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>61.5</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3883,7 +3739,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.14e-07</t>
+          <t>0.2989</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3751,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3907,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.268</v>
+        <v>1.542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.042</v>
+        <v>0.282</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -3923,7 +3779,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3935,10 +3791,10 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.245</v>
       </c>
       <c r="F19" t="n">
-        <v>0.061</v>
+        <v>0.083</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3946,70 +3802,6 @@
         </is>
       </c>
       <c r="H19" t="inlineStr">
-        <is>
-          <t>0.2989</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6E</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6E</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>0.0115</t>
         </is>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h after seeding, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control. The experiment was performed three times; these are the four wells of one experiment.</t>
+          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3044,7 +3044,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3056,13 +3056,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>97.47596153846155</v>
+        <v>97.3063973063973</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3074,13 +3074,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>102.6442307692308</v>
+        <v>103.7037037037037</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3092,13 +3092,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>98.4375</v>
+        <v>97.97979797979798</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3110,13 +3110,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>101.4423076923077</v>
+        <v>101.010101010101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3128,13 +3128,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>59.85576923076923</v>
+        <v>113.8047138047138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3146,13 +3146,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>63.46153846153847</v>
+        <v>120.8754208754209</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3164,13 +3164,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>60.45673076923077</v>
+        <v>114.8148148148148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3182,6 +3182,150 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
+        <v>117.8451178451178</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>97.47596153846155</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>102.6442307692308</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>98.4375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>101.4423076923077</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>59.85576923076923</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>63.46153846153847</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>60.45673076923077</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>48 h</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
         <v>62.3798076923077</v>
       </c>
     </row>
@@ -3196,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3623,7 +3767,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>WST-1 viability 24 h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3638,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -3651,7 +3795,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>WST-1 viability 24 h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3663,10 +3807,10 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>61.5</v>
+        <v>116.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3675,19 +3819,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.14e-07</t>
+          <t>0.000243</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3696,13 +3840,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.268</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>0.042</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -3710,12 +3854,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>WST-1 viability 48 h</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3724,13 +3868,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.18</v>
+        <v>61.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.061</v>
+        <v>0.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3739,7 +3883,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>2.14e-07</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SOCE delta F340/F380</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3763,10 +3907,10 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1.542</v>
+        <v>0.268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.282</v>
+        <v>0.042</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -3779,7 +3923,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOCE delta F340/F380</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3791,17 +3935,81 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>two-tailed Student's t-test</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.2989</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SOCE delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6E</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SOCE delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
         <v>0.245</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>0.083</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>two-tailed Student's t-test</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>0.0115</t>
         </is>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 viability, four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
+          <t>WST-1 metabolic signal (not a direct cell count or viability measure), four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>viability_pct_of_control</t>
+          <t>signal_pct_of_control</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>WST-1 signal 24 h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WST-1 viability 24 h</t>
+          <t>WST-1 signal 24 h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3814,14 +3814,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.000243</t>
-        </is>
-      </c>
+          <t>descriptive only; four wells from one experiment</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3831,7 +3827,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>WST-1 signal 48 h</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3859,7 +3855,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WST-1 viability 48 h</t>
+          <t>WST-1 signal 48 h</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3878,14 +3874,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2.14e-07</t>
-        </is>
-      </c>
+          <t>descriptive only; four wells from one experiment</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" state="visible" r:id="rId2"/>
@@ -18,7 +14,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,10 +23,8 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -46,13 +39,7 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin"/>
       <right style="thin"/>
@@ -70,9 +57,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -187,72 +173,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -308,7 +236,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -317,13 +245,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -357,17 +285,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -422,8 +339,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -480,7 +395,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Relative expression per replicate (2^-ddCt) for the four targets plotted in Figure 6B.</t>
+          <t>Relative expression per replicate (2^-ddCt) for the four targets plotted in Figure 1B.</t>
         </is>
       </c>
     </row>
@@ -492,7 +407,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of 1.5 mM CaCl2. Both as delta(F340/F380) versus the preceding baseline. The three samples of each group come from three independent cultures. The control group is the non-targeting (scrambled) shRNA control.</t>
+          <t>Fura-2/AM data: three measurements per group at 72 h after transduction. The twelve ER-release and SOCE amplitudes agree with the original GraphPad Prism sekil_4.20_fura2.pzfx tables. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the original ratio/time tables are supplied separately. Figure 2C-D displays these amplitude measurements and reports two-tailed Student’s t-tests (ER release p = 0.299; Ca²⁺ readdition p = 0.0115). The source Prism graph annotation was corrected to the author-confirmed CPA concentration of 10 µM; trace data and axes were unchanged.</t>
         </is>
       </c>
     </row>
@@ -504,7 +419,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 metabolic signal (not a direct cell count or viability measure), four wells per group, normalised to the mean of the non-targeting (scrambled) shRNA control at the same time point. The experiment was performed three times; these are the four wells of one experiment.</t>
+          <t>WST-1 metabolic signal at 48 h, normalised to the non-targeting (scrambled) shRNA control; four wells per group from one available experiment.</t>
         </is>
       </c>
     </row>
@@ -516,7 +431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Group means, SEM and the statistical test behind every panel of Figure 6.</t>
+          <t>Group means and SEM for Figure 1A-C and Figure 2C-D, with the inferential tests reported in the manuscript. Fura-2 comparisons use two-tailed Student’s t-tests on three measurements per group.</t>
         </is>
       </c>
     </row>
@@ -545,7 +460,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -961,7 +876,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2142,7 +2057,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2754,7 +2669,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3006,7 +2921,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3016,8 +2931,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.890000104904175" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="3.559999942779541" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3044,7 +2965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3056,13 +2977,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>97.3063973063973</v>
+        <v>97.47596153846155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3074,13 +2995,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>103.7037037037037</v>
+        <v>102.6442307692308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3092,13 +3013,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>97.97979797979798</v>
+        <v>98.4375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3110,13 +3031,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>101.010101010101</v>
+        <v>101.4423076923077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3128,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>113.8047138047138</v>
+        <v>59.85576923076923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3146,13 +3067,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>120.8754208754209</v>
+        <v>63.46153846153847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3164,13 +3085,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>114.8148148148148</v>
+        <v>60.45673076923077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3182,155 +3103,11 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>117.8451178451178</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>97.47596153846155</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>102.6442307692308</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>98.4375</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>101.4423076923077</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>59.85576923076923</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>63.46153846153847</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" t="n">
-        <v>60.45673076923077</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
         <v>62.3798076923077</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3340,8 +3117,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.78000020980835" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="1.440000057220459" customWidth="1" min="4" max="4"/>
+    <col width="5.440000057220459" customWidth="1" min="5" max="5"/>
+    <col width="5.440000057220459" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="7.329999923706055" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3388,7 +3175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3410,13 +3197,11 @@
       <c r="F2" t="n">
         <v>0.0242</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3438,13 +3223,11 @@
       <c r="F3" t="n">
         <v>0.0129</v>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3466,13 +3249,11 @@
       <c r="F4" t="n">
         <v>0.0009</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3491,7 +3272,6 @@
       <c r="E5" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>one-way ANOVA on log2 values, Tukey post hoc</t>
@@ -3506,7 +3286,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3528,13 +3308,11 @@
       <c r="F6" t="n">
         <v>0.012</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3558,19 +3336,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.000303</t>
-        </is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.000908</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3592,13 +3368,11 @@
       <c r="F8" t="n">
         <v>0.015</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3622,19 +3396,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.000554</t>
-        </is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.001108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3656,13 +3428,11 @@
       <c r="F10" t="n">
         <v>0.043</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3686,19 +3456,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00114</t>
-        </is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00114</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3720,13 +3488,11 @@
       <c r="F12" t="n">
         <v>0.059</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3750,24 +3516,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>9.58e-05</t>
-        </is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.000383</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>1C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WST-1 signal 24 h</t>
+          <t>WST-1 signal 48 h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3782,20 +3546,18 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>1C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WST-1 signal 24 h</t>
+          <t>WST-1 signal 48 h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3807,27 +3569,26 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>116.8</v>
+        <v>61.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>descriptive only; four wells from one experiment</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Mean ± SEM; one experiment, four wells per group; no inferential test</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>2C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WST-1 signal 48 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3836,26 +3597,24 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>0.268</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+        <v>0.042</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>2C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WST-1 signal 48 h</t>
+          <t>ER Ca2+ release delta F340/F380</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3864,30 +3623,32 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>61.5</v>
+        <v>0.18</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8</v>
+        <v>0.061</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>descriptive only; four wells from one experiment</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>two-tailed Student's t-test; three measurements per group</t>
+        </is>
+      </c>
+      <c r="H17">
+        <v>0.298923</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>2D</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3899,23 +3660,21 @@
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.268</v>
+        <v>1.542</v>
       </c>
       <c r="F18" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+        <v>0.282</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6E</t>
+          <t>2D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ER Ca2+ release delta F340/F380</t>
+          <t>SOCE delta F340/F380</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3927,88 +3686,22 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.245</v>
       </c>
       <c r="F19" t="n">
-        <v>0.061</v>
+        <v>0.083</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.2989</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6E</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6E</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.0115</t>
-        </is>
+          <t>two-tailed Student's t-test; three measurements per group</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>0.01153657</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4222,7 +3915,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4313,6 +4006,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -383,7 +383,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Raw Ct values for the four SOCE-associated targets and GAPDH in shTDP-43 cells and the non-targeting (scrambled) shRNA control, four biological replicates per group, same RNA set; experiment window 03.06-10.07.2026.</t>
+          <t>Raw Ct values for the four SOCE-associated targets and GAPDH in shTDP-43 cells and the non-targeting (scrambled) shRNA control, n = 4, same RNA set; experiment window 03.06-10.07.2026.</t>
         </is>
       </c>
     </row>
@@ -407,7 +407,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM data: three measurements per group at 72 h after transduction. The twelve ER-release and SOCE amplitudes agree with the original GraphPad Prism sekil_4.20_fura2.pzfx tables. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the original ratio/time tables are supplied separately. Figure 2C-D displays these amplitude measurements and reports two-tailed Student’s t-tests (ER release p = 0.299; Ca²⁺ readdition p = 0.0115). The source Prism graph annotation was corrected to the author-confirmed CPA concentration of 10 µM; trace data and axes were unchanged.</t>
+          <t>Fura-2/AM data at 72 h after transduction (n = 3). The twelve ER-release and SOCE amplitudes agree with the original GraphPad Prism sekil_4.20_fura2.pzfx tables. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the original ratio/time tables are supplied separately. Figure 2C-D displays these amplitude measurements and reports two-tailed Student’s t-tests (ER release p = 0.299; Ca²⁺ readdition p = 0.0115). The source Prism graph annotation was corrected to the author-confirmed CPA concentration of 10 µM; trace data and axes were unchanged.</t>
         </is>
       </c>
     </row>
@@ -419,7 +419,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 metabolic signal at 48 h, normalised to the non-targeting (scrambled) shRNA control; four wells per group from one available experiment.</t>
+          <t>WST-1 metabolic signal at 48 h, normalised to the non-targeting (scrambled) shRNA control; n = 4.</t>
         </is>
       </c>
     </row>
@@ -431,7 +431,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Group means and SEM for Figure 1A-C and Figure 2C-D, with the inferential tests reported in the manuscript. Fura-2 comparisons use two-tailed Student’s t-tests on three measurements per group.</t>
+          <t>Group means and SEM for Figure 1A-C and Figure 2C-D, with the inferential tests reported in the manuscript. Fura-2 comparisons use two-tailed Student’s t-tests (n = 3).</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mean ± SEM; one experiment, four wells per group; no inferential test</t>
+          <t>Mean ± SEM; n = 4; no inferential test</t>
         </is>
       </c>
     </row>
@@ -3633,10 +3633,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test; three measurements per group</t>
-        </is>
-      </c>
-      <c r="H17">
+          <t>two-tailed Student's t-test; n = 3</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>0.298923</v>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test; three measurements per group</t>
-        </is>
-      </c>
-      <c r="H19">
+          <t>two-tailed Student's t-test; n = 3</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>0.01153657</v>
       </c>
     </row>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -2,6 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" state="visible" r:id="rId2"/>
@@ -14,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,8 +28,10 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,7 +46,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
@@ -57,8 +70,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -173,14 +187,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -236,7 +308,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -245,13 +317,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -285,6 +357,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -339,6 +422,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -371,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RT-qPCR of TARDBP in three groups, four biological replicates each; raw Ct for TARDBP and GAPDH, dCt, ddCt and 2^-ddCt. Experiment dates 14.04-21.05.2026.</t>
+          <t>RT-qPCR of TARDBP in three groups (n = 4 each); raw Ct for TARDBP and GAPDH, dCt, ddCt and 2^-ddCt. Experiment dates 14.04-21.05.2026.</t>
         </is>
       </c>
     </row>
@@ -407,7 +492,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM data at 72 h after transduction (n = 3). The twelve ER-release and SOCE amplitudes agree with the original GraphPad Prism sekil_4.20_fura2.pzfx tables. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the original ratio/time tables are supplied separately. Figure 2C-D displays these amplitude measurements and reports two-tailed Student’s t-tests (ER release p = 0.299; Ca²⁺ readdition p = 0.0115). The source Prism graph annotation was corrected to the author-confirmed CPA concentration of 10 µM; trace data and axes were unchanged.</t>
+          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of nominally 1.5 mM CaCl2. Both are peak delta(F340/F380) versus the preceding baseline (n = 3, descriptive). The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; original ratio/time tables are supplied separately. Only the CPA annotation was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</t>
         </is>
       </c>
     </row>
@@ -419,7 +504,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 metabolic signal at 48 h, normalised to the non-targeting (scrambled) shRNA control; n = 4.</t>
+          <t>WST-1 metabolic signal at 48 h (n = 4; not a direct cell count or viability measure), normalised to the mean of the non-targeting (scrambled) shRNA control.</t>
         </is>
       </c>
     </row>
@@ -431,7 +516,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Group means and SEM for Figure 1A-C and Figure 2C-D, with the inferential tests reported in the manuscript. Fura-2 comparisons use two-tailed Student’s t-tests (n = 3).</t>
+          <t>Group means, SEM and the statistical test behind Figures 1 and 2.</t>
         </is>
       </c>
     </row>
@@ -460,7 +545,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -876,7 +961,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2057,7 +2142,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2669,7 +2754,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2921,7 +3006,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2933,12 +3018,6 @@
   </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.890000104904175" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="3.559999942779541" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3107,7 +3186,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3119,16 +3198,6 @@
   </sheetPr>
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4.78000020980835" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="1.440000057220459" customWidth="1" min="4" max="4"/>
-    <col width="5.440000057220459" customWidth="1" min="5" max="5"/>
-    <col width="5.440000057220459" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="7.329999923706055" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3197,6 +3266,8 @@
       <c r="F2" t="n">
         <v>0.0242</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3223,6 +3294,8 @@
       <c r="F3" t="n">
         <v>0.0129</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3249,6 +3322,8 @@
       <c r="F4" t="n">
         <v>0.0009</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3272,6 +3347,7 @@
       <c r="E5" t="n">
         <v>94.40000000000001</v>
       </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>one-way ANOVA on log2 values, Tukey post hoc</t>
@@ -3308,6 +3384,8 @@
       <c r="F6" t="n">
         <v>0.012</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3339,8 +3417,10 @@
           <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0.000908</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.000907664</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3368,6 +3448,8 @@
       <c r="F8" t="n">
         <v>0.015</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3399,8 +3481,10 @@
           <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0.001108</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00110869</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3428,6 +3512,8 @@
       <c r="F10" t="n">
         <v>0.043</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3459,8 +3545,10 @@
           <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0.00114</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00113901</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -3488,6 +3576,8 @@
       <c r="F12" t="n">
         <v>0.059</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3519,8 +3609,10 @@
           <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0.000383</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.000383066</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -3548,6 +3640,8 @@
       <c r="F14" t="n">
         <v>1.2</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3576,9 +3670,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mean ± SEM; n = 4; no inferential test</t>
-        </is>
-      </c>
+          <t>descriptive only; four wells from one experiment</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3605,6 +3700,8 @@
       <c r="F16" t="n">
         <v>0.042</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3633,12 +3730,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test; n = 3</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>0.298923</v>
-      </c>
+          <t>descriptive; n = 3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3665,6 +3760,8 @@
       <c r="F18" t="n">
         <v>0.282</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3693,15 +3790,13 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>two-tailed Student's t-test; n = 3</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>0.01153657</v>
-      </c>
+          <t>descriptive; n = 3</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3915,7 +4010,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4006,6 +4101,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -12,10 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_Ct" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_rel" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2_per_culture" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,56 +493,159 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of nominally 1.5 mM CaCl2. Both are peak delta(F340/F380) versus the preceding baseline (n = 3, descriptive). The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; original ratio/time tables are supplied separately. Only the CPA annotation was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</t>
+          <t>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of nominally 1.5 mM CaCl2. Both are peak delta(F340/F380) versus the preceding baseline; n = 3 independent cultures per group, and replicate i of both phases is the same recording. The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the exported ratio/time tables of these two recordings are in source_data/fura2_traces of the repository and are replotted in Figure 2E. Only the CPA annotation was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WST1</t>
+          <t>Fura2_per_culture</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WST-1 metabolic signal at 48 h (n = 4; not a direct cell count or viability measure), normalised to the mean of the non-targeting (scrambled) shRNA control.</t>
+          <t>Both Fura-2 phases per culture with the readdition-to-release ratio of that culture.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Summary_stats</t>
+          <t>WST1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Group means, SEM and the statistical test behind Figures 1 and 2.</t>
+          <t>WST-1 metabolic signal at 48 h (n = 4; not a direct cell count or viability measure), normalised to the mean of the non-targeting (scrambled) shRNA control.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Primers</t>
+          <t>Summary_stats</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Primer sequences, product sizes and annealing temperatures for the RT-qPCR targets and the GAPDH reference.</t>
+          <t>Group means, SEM and the statistical tests behind Figures 1 and 2, including the Welch tests and 95% CIs of the Fura-2 amplitudes.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Primers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Primer sequences, product sizes and annealing temperatures for the RT-qPCR targets and the GAPDH reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Thermal_profile</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Thermal cycling profile of the RT-qPCR reactions.</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>thermal_condition</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Initial denaturation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>95 °C, 5 min</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Amplification</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>95 °C 10 s; annealing 57 or 60 °C 20 s (per gene); 72 °C 10 s</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Extension</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>72 °C, 10 min</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Melt curve</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>95 °C 10 s; 63 °C 15 s; continuous ramp to 95 °C</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3016,173 +3120,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>group</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>ER_release</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>signal_pct_of_control</t>
+          <t>readdition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>readdition_to_release_ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.347946</v>
       </c>
       <c r="D2" t="n">
-        <v>97.47596153846155</v>
+        <v>1.975406</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5.677334988762625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0.2076459999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>102.6442307692308</v>
+        <v>1.637851</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.887707925989428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>0.248497</v>
       </c>
       <c r="D4" t="n">
-        <v>98.4375</v>
+        <v>1.013373</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.07800899004817</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0.05909500000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>101.4423076923077</v>
+        <v>0.08027300000000004</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.35837211269989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.2290789999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>59.85576923076923</v>
+        <v>0.316517</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.381693651535061</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0.2520519999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>63.46153846153847</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>60.45673076923077</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>48 h</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>62.3798076923077</v>
+        <v>0.338355</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.342401567930427</v>
       </c>
     </row>
   </sheetData>
@@ -3196,604 +3275,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>panel</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>measurement</t>
+          <t>group</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>well</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>SEM</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>p_value</t>
+          <t>signal_pct_of_control</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TARDBP relative expression</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Untransduced control</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.0009</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>97.47596153846155</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TARDBP relative expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9301</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0129</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>102.6442307692308</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TARDBP relative expression</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0519</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0009</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>98.4375</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TARDBP silencing</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>shTDP-43 vs controls</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>one-way ANOVA on log2 values, Tukey post hoc</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.36e-15</t>
-        </is>
+        <v>101.4423076923077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TRPC1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>59.85576923076923</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TRPC1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.819</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.000907664</t>
-        </is>
+        <v>63.46153846153847</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STIM1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>60.45673076923077</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>48 h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STIM1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.00110869</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ORAI1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ORAI1 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.00113901</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ATP2A3 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ATP2A3 relative mRNA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.000383066</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1C</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WST-1 signal 48 h</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>100</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1C</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>WST-1 signal 48 h</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>descriptive only; four wells from one experiment</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ER Ca2+ release delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2C</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ER Ca2+ release delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>descriptive; n = 3</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2D</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Non-targeting shRNA control</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2D</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SOCE delta F340/F380</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>shTDP-43</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>descriptive; n = 3</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>62.3798076923077</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3806,208 +3455,672 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>accession</t>
+          <t>panel</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>gene</t>
+          <t>measurement</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>forward_primer_5_3</t>
+          <t>group</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reverse_primer_5_3</t>
+          <t>n</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>product_size_bp</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>annealing_temperature_C</t>
+          <t>SEM</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NM_007375.4</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TARDBP</t>
+          <t>TARDBP relative expression</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GATGGTGTGACTGCAAACTTC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CAGCTCATCCTCAGTCATGTC</t>
-        </is>
+          <t>Untransduced control</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>110</v>
+        <v>1.0009</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
-      </c>
+        <v>0.0242</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NM_003156.4</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STIM1</t>
+          <t>TARDBP relative expression</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AGCAGAGTTTTGCCGAATTG</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ATCACTTTCTTCCACATCCACAT</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>0.9301</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
-      </c>
+        <v>0.0129</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NM_032790.4</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORAI1</t>
+          <t>TARDBP relative expression</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAGAGTTACTCCGAGGTGATGAG</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>GAGAGCAGAGCCGAGGTCC</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>0.0519</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
-      </c>
+        <v>0.0009</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NM_003304.5</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRPC1</t>
+          <t>TARDBP silencing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TGCGACAAGGGTGACTATTA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TCCATTAGTTTCTGACAACCG</t>
-        </is>
+          <t>shTDP-43 vs controls</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>176</v>
-      </c>
-      <c r="F5" t="n">
-        <v>57</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>one-way ANOVA on log2 values, Tukey post hoc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.36e-15</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NM_005173.4</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ATP2A3 (SERCA3)</t>
+          <t>TRPC1 relative mRNA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GTCATCAACATCGGCCACTT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>GCCAGGCATGTAGTGATGAC</t>
-        </is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
-      </c>
+        <v>0.012</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NM_002046.7</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GAPDH</t>
+          <t>TRPC1 relative mRNA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CAGTCAGCCGCATCTTCTTT</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GCCCAATACGACCAAATCC</t>
-        </is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>192</v>
+        <v>1.819</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
-      </c>
+        <v>0.109</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.000907664</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>STIM1 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>STIM1 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.00110869</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ORAI1 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ORAI1 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.00113901</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ATP2A3 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ATP2A3 relative mRNA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>two-tailed Student's t-test; Holm-adjusted across four targets</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.000383066</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WST-1 signal 48 h</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WST-1 signal 48 h</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>descriptive only; four wells from one experiment</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ER Ca2+ release delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ER Ca2+ release delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Welch's two-tailed t-test, n = 3 independent cultures per group; difference −0.09, 95% CI −0.30 to +0.13</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.307</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SOCE delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SOCE delta F340/F380</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Welch's two-tailed t-test, n = 3 independent cultures per group; difference −1.30, 95% CI −2.40 to −0.19</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.0354</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2C-D</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>readdition/ER release ratio per culture</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Non-targeting shRNA control</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2C-D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>readdition/ER release ratio per culture</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>shTDP-43</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>descriptive; ratio of the two phases of the same recording</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4020,84 +4133,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>accession</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>thermal_condition</t>
+          <t>gene</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>cycles</t>
+          <t>forward_primer_5_3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>reverse_primer_5_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>product_size_bp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>annealing_temperature_C</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Initial denaturation</t>
+          <t>NM_007375.4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95 °C, 5 min</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
+          <t>TARDBP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GATGGTGTGACTGCAAACTTC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CAGCTCATCCTCAGTCATGTC</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Amplification</t>
+          <t>NM_003156.4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95 °C 10 s; annealing 57 or 60 °C 20 s (per gene); 72 °C 10 s</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>40</v>
+          <t>STIM1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGCAGAGTTTTGCCGAATTG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ATCACTTTCTTCCACATCCACAT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>NM_032790.4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>72 °C, 10 min</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
+          <t>ORAI1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CAGAGTTACTCCGAGGTGATGAG</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GAGAGCAGAGCCGAGGTCC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>119</v>
+      </c>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Melt curve</t>
+          <t>NM_003304.5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95 °C 10 s; 63 °C 15 s; continuous ramp to 95 °C</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
+          <t>TRPC1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TGCGACAAGGGTGACTATTA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TCCATTAGTTTCTGACAACCG</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>176</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NM_005173.4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ATP2A3 (SERCA3)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GTCATCAACATCGGCCACTT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GCCAGGCATGTAGTGATGAC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>143</v>
+      </c>
+      <c r="F6" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NM_002046.7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GAPDH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CAGTCAGCCGCATCTTCTTT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GCCCAATACGACCAAATCC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>192</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R95e40bd4239747cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" r:id="Rb3f2bb48286c4a6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_Ct" sheetId="3" r:id="R810899bfcb6646b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_rel" sheetId="4" r:id="R9da9557cf96a4235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2" sheetId="5" r:id="R5684274583bc4c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2_per_culture" sheetId="6" r:id="R9c9699f564894882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="7" r:id="R965dd31cc9214072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="8" r:id="Rc7cb3078d91b48b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="9" r:id="Raec4bed26f20458d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="10" r:id="R9c2d4384cd5d4b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfea85f52ca28460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" r:id="R7c2df2afb1c84419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_Ct" sheetId="3" r:id="R4af313dab1a4431f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_rel" sheetId="4" r:id="R77a197d572a34471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2" sheetId="5" r:id="R73bcd9c3a3764a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2_per_culture" sheetId="6" r:id="R08939f0ae4a04223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="7" r:id="Rf057bebe82ad41d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="8" r:id="R93b62c8385194994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="9" r:id="R0afadc900880405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="10" r:id="R0947345709e041d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,10 +52,16 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -347,6 +353,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="inlineStr">
@@ -360,103 +370,97 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="65" customHeight="1">
       <x:c r="A2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TARDBP_qPCR</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RT-qPCR of TARDBP in three groups (n = 4 each); raw Ct for TARDBP and GAPDH, dCt, ddCt and 2^-ddCt. Experiment dates 14.04-21.05.2026.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="B2" s="2" t="str">
+        <x:v>TARDBP RT-qPCR: four technical measurements of the same biological sample per group. Raw Ct, dCt, ddCt and 2^-ddCt are retained. Recorded assay dates do not identify independent cultures.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="65" customHeight="1">
       <x:c r="A3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Target_qPCR_Ct</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Raw Ct values for the four SOCE-associated targets and GAPDH in shTDP-43 cells and the non-targeting (scrambled) shRNA control, n = 4, same RNA set; experiment window 03.06-10.07.2026.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="B3" s="2" t="str">
+        <x:v>Four target genes: raw target and GAPDH Ct values. Four measurements per group are technical repeats of the same biological sample, not independent RNA isolations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="65" customHeight="1">
       <x:c r="A4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Target_qPCR_rel</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Relative expression per replicate (2^-ddCt) for the four targets plotted in Figure 1B.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="B4" s="2" t="str">
+        <x:v>Relative expression values plotted in Figure 1B. Four technical measurements per target and group; descriptive only.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="180" customHeight="1">
       <x:c r="A5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fura2</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B5" s="2" t="str">
         <x:v>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of nominally 1.5 mM CaCl2. Both are peak delta(F340/F380) versus the preceding baseline; three wells per group from one culture plate, and well i of both phases is the same recording. This is one biological experiment; the well comparison is descriptive. The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the exported ratio/time tables of these two recordings are in source_data/fura2_traces of the repository and are replotted in Figure 2E. Only the CPA annotation was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="65" customHeight="1">
       <x:c r="A6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fura2_per_culture</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="2" t="str">
         <x:v>Both Fura-2 phases per well with the readdition-to-release ratio of that well; one culture plate only. The sheet name is historical.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="65" customHeight="1">
       <x:c r="A7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">WST1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" t="inlineStr">
+      <x:c r="B7" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">WST-1 metabolic signal at 48 h (n = 4; not a direct cell count or viability measure), normalised to the mean of the non-targeting (scrambled) shRNA control.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="65" customHeight="1">
       <x:c r="A8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Summary_stats</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>Group means and well-to-well SEM behind Figures 1 and 2; the Fura-2 and WST-1 comparisons are descriptive only.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="B8" s="2" t="str">
+        <x:v>Group means and technical-repeat or well-to-well SEM. All laboratory comparisons are descriptive; no inferential p values are reported.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="65" customHeight="1">
       <x:c r="A9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Primers</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" t="inlineStr">
+      <x:c r="B9" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Primer sequences, product sizes and annealing temperatures for the RT-qPCR targets and the GAPDH reference.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="65" customHeight="1">
       <x:c r="A10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Thermal_profile</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" t="inlineStr">
+      <x:c r="B10" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Thermal cycling profile of the RT-qPCR reactions.</x:t>
         </x:is>
@@ -563,10 +567,8 @@
           <x:t xml:space="preserve">group</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">replicate</x:t>
-        </x:is>
+      <x:c r="B1" s="1" t="str">
+        <x:v>technical_repeat</x:v>
       </x:c>
       <x:c r="C1" s="1" t="inlineStr">
         <x:is>
@@ -979,10 +981,8 @@
           <x:t xml:space="preserve">group</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">replicate</x:t>
-        </x:is>
+      <x:c r="C1" s="1" t="str">
+        <x:v>technical_repeat</x:v>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
@@ -2155,10 +2155,8 @@
           <x:t xml:space="preserve">group</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">replicate</x:t>
-        </x:is>
+      <x:c r="C1" s="1" t="str">
+        <x:v>technical_repeat</x:v>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
@@ -3320,6 +3318,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="7" max="7" width="58" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="inlineStr">
@@ -3352,7 +3360,7 @@
           <x:t xml:space="preserve">SEM</x:t>
         </x:is>
       </x:c>
-      <x:c r="G1" s="1" t="inlineStr">
+      <x:c r="G1" s="3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">test</x:t>
         </x:is>
@@ -3363,7 +3371,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1A</x:t>
@@ -3388,18 +3396,12 @@
       <x:c r="F2" t="n">
         <x:v>0.0242</x:v>
       </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="G2" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H2"/>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
       <x:c r="A3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1A</x:t>
@@ -3424,18 +3426,12 @@
       <x:c r="F3" t="n">
         <x:v>0.0129</x:v>
       </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="G3" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H3"/>
+    </x:row>
+    <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1A</x:t>
@@ -3460,18 +3456,12 @@
       <x:c r="F4" t="n">
         <x:v>0.0009</x:v>
       </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="G4" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H4"/>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1A</x:t>
@@ -3498,18 +3488,12 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">one-way ANOVA on log2 values, Tukey post hoc</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2.36e-15</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="G5" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H5"/>
+    </x:row>
+    <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3534,18 +3518,12 @@
       <x:c r="F6" t="n">
         <x:v>0.012</x:v>
       </x:c>
-      <x:c r="G6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="G6" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H6"/>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3570,18 +3548,12 @@
       <x:c r="F7" t="n">
         <x:v>0.109</x:v>
       </x:c>
-      <x:c r="G7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">two-tailed Student's t-test; Holm-adjusted across four targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.000907664</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+      <x:c r="G7" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H7"/>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
       <x:c r="A8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3606,18 +3578,12 @@
       <x:c r="F8" t="n">
         <x:v>0.015</x:v>
       </x:c>
-      <x:c r="G8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="G8" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H8"/>
+    </x:row>
+    <x:row r="9" ht="38" customHeight="1">
       <x:c r="A9" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3642,18 +3608,12 @@
       <x:c r="F9" t="n">
         <x:v>0.132</x:v>
       </x:c>
-      <x:c r="G9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">two-tailed Student's t-test; Holm-adjusted across four targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.00110869</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+      <x:c r="G9" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H9"/>
+    </x:row>
+    <x:row r="10" ht="38" customHeight="1">
       <x:c r="A10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3678,18 +3638,12 @@
       <x:c r="F10" t="n">
         <x:v>0.043</x:v>
       </x:c>
-      <x:c r="G10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+      <x:c r="G10" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H10"/>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
       <x:c r="A11" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3714,18 +3668,12 @@
       <x:c r="F11" t="n">
         <x:v>0.108</x:v>
       </x:c>
-      <x:c r="G11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">two-tailed Student's t-test; Holm-adjusted across four targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.00113901</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+      <x:c r="G11" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H11"/>
+    </x:row>
+    <x:row r="12" ht="38" customHeight="1">
       <x:c r="A12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3750,18 +3698,12 @@
       <x:c r="F12" t="n">
         <x:v>0.059</x:v>
       </x:c>
-      <x:c r="G12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="H12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+      <x:c r="G12" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H12"/>
+    </x:row>
+    <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1B</x:t>
@@ -3786,18 +3728,12 @@
       <x:c r="F13" t="n">
         <x:v>0.233</x:v>
       </x:c>
-      <x:c r="G13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">two-tailed Student's t-test; Holm-adjusted across four targets</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.000383066</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+      <x:c r="G13" s="2" t="str">
+        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
+      </x:c>
+      <x:c r="H13"/>
+    </x:row>
+    <x:row r="14" ht="38" customHeight="1">
       <x:c r="A14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1C</x:t>
@@ -3822,7 +3758,7 @@
       <x:c r="F14" t="n">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="G14" t="inlineStr">
+      <x:c r="G14" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -3833,7 +3769,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="38" customHeight="1">
       <x:c r="A15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1C</x:t>
@@ -3858,7 +3794,7 @@
       <x:c r="F15" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="G15" t="inlineStr">
+      <x:c r="G15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">descriptive only; four wells from one experiment</x:t>
         </x:is>
@@ -3869,7 +3805,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="38" customHeight="1">
       <x:c r="A16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2C</x:t>
@@ -3894,7 +3830,7 @@
       <x:c r="F16" t="n">
         <x:v>0.042</x:v>
       </x:c>
-      <x:c r="G16" t="inlineStr">
+      <x:c r="G16" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -3905,7 +3841,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="38" customHeight="1">
       <x:c r="A17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2C</x:t>
@@ -3930,12 +3866,12 @@
       <x:c r="F17" t="n">
         <x:v>0.061</x:v>
       </x:c>
-      <x:c r="G17" t="str">
+      <x:c r="G17" s="2" t="str">
         <x:v>descriptive only; three wells per group on one culture plate</x:v>
       </x:c>
       <x:c r="H17"/>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="38" customHeight="1">
       <x:c r="A18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2D</x:t>
@@ -3960,7 +3896,7 @@
       <x:c r="F18" t="n">
         <x:v>0.282</x:v>
       </x:c>
-      <x:c r="G18" t="inlineStr">
+      <x:c r="G18" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -3971,7 +3907,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="38" customHeight="1">
       <x:c r="A19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2D</x:t>
@@ -3996,12 +3932,12 @@
       <x:c r="F19" t="n">
         <x:v>0.083</x:v>
       </x:c>
-      <x:c r="G19" t="str">
+      <x:c r="G19" s="2" t="str">
         <x:v>descriptive only; three wells per group on one culture plate</x:v>
       </x:c>
       <x:c r="H19"/>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="38" customHeight="1">
       <x:c r="A20" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2C-D</x:t>
@@ -4024,7 +3960,7 @@
       <x:c r="F20" t="n">
         <x:v>1.1</x:v>
       </x:c>
-      <x:c r="G20" t="inlineStr">
+      <x:c r="G20" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
@@ -4035,7 +3971,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="38" customHeight="1">
       <x:c r="A21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2C-D</x:t>
@@ -4058,7 +3994,7 @@
       <x:c r="F21" t="n">
         <x:v>0.01</x:v>
       </x:c>
-      <x:c r="G21" t="inlineStr">
+      <x:c r="G21" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">descriptive; ratio of the two phases of the same recording</x:t>
         </x:is>

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rfea85f52ca28460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" r:id="R7c2df2afb1c84419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_Ct" sheetId="3" r:id="R4af313dab1a4431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_rel" sheetId="4" r:id="R77a197d572a34471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2" sheetId="5" r:id="R73bcd9c3a3764a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2_per_culture" sheetId="6" r:id="R08939f0ae4a04223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="7" r:id="Rf057bebe82ad41d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="8" r:id="R93b62c8385194994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="9" r:id="R0afadc900880405b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="10" r:id="R0947345709e041d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R1bf261c67abb4b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TARDBP_qPCR" sheetId="2" r:id="Ra48d13d160534528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_Ct" sheetId="3" r:id="Rec2fdaf19d7c45c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_qPCR_rel" sheetId="4" r:id="Rb70280b497054470"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2" sheetId="5" r:id="R664a73f6298544a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fura2_per_culture" sheetId="6" r:id="R3308f63c9e284bb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WST1" sheetId="7" r:id="R712e6cbd67fd4ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary_stats" sheetId="8" r:id="Rf4f8e8792d7f4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primers" sheetId="9" r:id="R06f1f02d1e634ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermal_profile" sheetId="10" r:id="R205bdf77d7d54127"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,6 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.00E+00"/>
+  </x:numFmts>
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
@@ -52,7 +55,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top"/>
@@ -63,6 +66,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -377,7 +381,7 @@
         </x:is>
       </x:c>
       <x:c r="B2" s="2" t="str">
-        <x:v>TARDBP RT-qPCR: four technical measurements of the same biological sample per group. Raw Ct, dCt, ddCt and 2^-ddCt are retained. Recorded assay dates do not identify independent cultures.</x:v>
+        <x:v>TARDBP RT-qPCR: four biological replicates per group. Raw Ct, dCt, ddCt and 2^-ddCt are retained.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="65" customHeight="1">
@@ -387,7 +391,7 @@
         </x:is>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>Four target genes: raw target and GAPDH Ct values. Four measurements per group are technical repeats of the same biological sample, not independent RNA isolations.</x:v>
+        <x:v>Four target genes: raw target and GAPDH Ct values from four biological replicates per group. The target-gene assays share an RNA set; TARDBP uses a separate set.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="65" customHeight="1">
@@ -397,7 +401,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>Relative expression values plotted in Figure 1B. Four technical measurements per target and group; descriptive only.</x:v>
+        <x:v>Relative expression values plotted in Figure 1B. Four biological replicates per target and group.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="180" customHeight="1">
@@ -439,7 +443,7 @@
         </x:is>
       </x:c>
       <x:c r="B8" s="2" t="str">
-        <x:v>Group means and technical-repeat or well-to-well SEM. All laboratory comparisons are descriptive; no inferential p values are reported.</x:v>
+        <x:v>Group means and SEM across biological replicates for RT-qPCR. Two-sided Welch tests on dCt; Holm correction across four targets and separately across two TARDBP contrasts. Fura-2 and WST-1 summaries describe well-to-well variation only.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="65" customHeight="1">
@@ -560,6 +564,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="inlineStr">
@@ -568,7 +575,7 @@
         </x:is>
       </x:c>
       <x:c r="B1" s="1" t="str">
-        <x:v>technical_repeat</x:v>
+        <x:v>biological_replicate</x:v>
       </x:c>
       <x:c r="C1" s="1" t="inlineStr">
         <x:is>
@@ -969,6 +976,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="inlineStr">
@@ -982,7 +992,7 @@
         </x:is>
       </x:c>
       <x:c r="C1" s="1" t="str">
-        <x:v>technical_repeat</x:v>
+        <x:v>biological_replicate</x:v>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
@@ -2143,6 +2153,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="inlineStr">
@@ -2156,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c r="C1" s="1" t="str">
-        <x:v>technical_repeat</x:v>
+        <x:v>biological_replicate</x:v>
       </x:c>
       <x:c r="D1" s="1" t="inlineStr">
         <x:is>
@@ -3397,9 +3410,9 @@
         <x:v>0.0242</x:v>
       </x:c>
       <x:c r="G2" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H2"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H2" s="4"/>
     </x:row>
     <x:row r="3" ht="38" customHeight="1">
       <x:c r="A3" t="inlineStr">
@@ -3427,9 +3440,9 @@
         <x:v>0.0129</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H3"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H3" s="4"/>
     </x:row>
     <x:row r="4" ht="38" customHeight="1">
       <x:c r="A4" t="inlineStr">
@@ -3457,9 +3470,9 @@
         <x:v>0.0009</x:v>
       </x:c>
       <x:c r="G4" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H4"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H4" s="4"/>
     </x:row>
     <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" t="inlineStr">
@@ -3489,9 +3502,11 @@
         </x:is>
       </x:c>
       <x:c r="G5" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H5"/>
+        <x:v>Welch dCt; max Holm-adjusted p of two TARDBP contrasts</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="n">
+        <x:v>3.1995558426905583e-10</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" t="inlineStr">
@@ -3519,9 +3534,9 @@
         <x:v>0.012</x:v>
       </x:c>
       <x:c r="G6" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H6"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H6" s="4"/>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" t="inlineStr">
@@ -3549,9 +3564,11 @@
         <x:v>0.109</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H7"/>
+        <x:v>two-sided Welch dCt; Holm-adjusted across four targets</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="n">
+        <x:v>0.003961679552801206</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="38" customHeight="1">
       <x:c r="A8" t="inlineStr">
@@ -3579,9 +3596,9 @@
         <x:v>0.015</x:v>
       </x:c>
       <x:c r="G8" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H8"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H8" s="4"/>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
       <x:c r="A9" t="inlineStr">
@@ -3609,9 +3626,11 @@
         <x:v>0.132</x:v>
       </x:c>
       <x:c r="G9" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H9"/>
+        <x:v>two-sided Welch dCt; Holm-adjusted across four targets</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="n">
+        <x:v>0.003961679552801206</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
       <x:c r="A10" t="inlineStr">
@@ -3639,9 +3658,9 @@
         <x:v>0.043</x:v>
       </x:c>
       <x:c r="G10" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H10"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H10" s="4"/>
     </x:row>
     <x:row r="11" ht="38" customHeight="1">
       <x:c r="A11" t="inlineStr">
@@ -3669,9 +3688,11 @@
         <x:v>0.108</x:v>
       </x:c>
       <x:c r="G11" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H11"/>
+        <x:v>two-sided Welch dCt; Holm-adjusted across four targets</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="n">
+        <x:v>0.0026092887594562526</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="38" customHeight="1">
       <x:c r="A12" t="inlineStr">
@@ -3699,9 +3720,9 @@
         <x:v>0.059</x:v>
       </x:c>
       <x:c r="G12" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H12"/>
+        <x:v>four biological replicates per group; mean and SEM</x:v>
+      </x:c>
+      <x:c r="H12" s="4"/>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" t="inlineStr">
@@ -3729,9 +3750,11 @@
         <x:v>0.233</x:v>
       </x:c>
       <x:c r="G13" s="2" t="str">
-        <x:v>descriptive only; four technical RT-qPCR repeats per group</x:v>
-      </x:c>
-      <x:c r="H13"/>
+        <x:v>two-sided Welch dCt; Holm-adjusted across four targets</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="n">
+        <x:v>0.0000676605356856677</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="38" customHeight="1">
       <x:c r="A14" t="inlineStr">

--- a/supplementary/S1_laboratory_source_data.xlsx
+++ b/supplementary/S1_laboratory_source_data.xlsx
@@ -404,14 +404,14 @@
         <x:v>Relative expression values plotted in Figure 1B. Four biological replicates per target and group.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="180" customHeight="1">
+    <x:row r="5" ht="235" customHeight="1">
       <x:c r="A5" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fura2</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; SOCE is the rise after re-addition of nominally 1.5 mM CaCl2. Both are peak delta(F340/F380) versus the preceding baseline; three wells per group from one culture plate, and well i of both phases is the same recording. This is one biological experiment; the well comparison is descriptive. The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Figure 2A-B uses unredrawn graphs exported from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the exported ratio/time tables of these two recordings are in source_data/fura2_traces of the repository and are replotted in Figure 2E. Only the CPA annotation was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</x:v>
+        <x:v>Fura-2/AM measurements. ER Ca2+ release is the rise in F340/F380 after 10 uM cyclopiazonic acid in Ca2+-free HBS with EGTA; the Ca2+-readdition response (labelled 'SOCE' in the measurement column of this sheet) is the rise after re-addition of nominally 1.5 mM CaCl2. The Fura-2 ratio records net cytosolic Ca2+ accumulation and does not isolate membrane influx from extrusion or ER re-uptake. Both are peak delta(F340/F380) versus the preceding baseline; three wells per group from one culture plate, and well i of both phases is the same recording. This is one biological experiment; the well comparison is descriptive. The control group is the non-targeting (scrambled) shRNA control. The original Prism amplitude table is sekil_4.20_fura2.pzfx. Supplementary Figure S9 shows the two representative recordings as exported, unredrawn, from the original trace project Elmas_130626_Ca2_Trase_Grafikleri.pzf; the exported ratio/time tables of these two recordings are in source_data/fura2_traces of the repository and are replotted on common axes in Figure 2A, aligned to the steepest point of the readdition rise, with no value smoothed or rescaled. Only the CPA annotation of the export was corrected to the author-confirmed 10 uM; trace data and axes were unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="65" customHeight="1">
